--- a/game_config/Datas/SkillEffectConfig.xlsx
+++ b/game_config/Datas/SkillEffectConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\gitee\TiangZ\game_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF885CB6-CF08-4905-8424-ECFCE8EAF494}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90C6ED9B-FFAD-4A05-8278-CC611A4636B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="46">
   <si>
     <t>##var</t>
   </si>
@@ -142,12 +142,6 @@
   </si>
   <si>
     <t>给主目标添加真言术·韧</t>
-  </si>
-  <si>
-    <t>Heal</t>
-  </si>
-  <si>
-    <t>每跳为主目标恢复30点生命</t>
   </si>
   <si>
     <t>PrimaryTarget</t>
@@ -162,6 +156,18 @@
   </si>
   <si>
     <t>每跳对主目标造成20点暗影伤害</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Caster</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AddBuff</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>给自己添加24秒恢复Buff</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -760,16 +766,16 @@
         <v>1</v>
       </c>
       <c r="E13" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="F13" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="G13">
-        <v>30</v>
+        <v>2002</v>
       </c>
       <c r="H13" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -783,16 +789,16 @@
         <v>1</v>
       </c>
       <c r="E14" t="s">
+        <v>39</v>
+      </c>
+      <c r="F14" t="s">
+        <v>40</v>
+      </c>
+      <c r="G14" t="s">
         <v>41</v>
       </c>
-      <c r="F14" t="s">
+      <c r="H14" t="s">
         <v>42</v>
-      </c>
-      <c r="G14" t="s">
-        <v>43</v>
-      </c>
-      <c r="H14" t="s">
-        <v>44</v>
       </c>
     </row>
   </sheetData>
